--- a/Student_Performance_2026.xlsx
+++ b/Student_Performance_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andi/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andi/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{1C14CFC7-B07A-B640-8F39-7D3157095828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CDE124D-E4C8-C645-8D0F-88E2027390D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4020" yWindow="1280" windowWidth="25380" windowHeight="16700" activeTab="2" xr2:uid="{E191524F-50CC-4647-A13F-E35264F811B6}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17180" activeTab="2" xr2:uid="{E191524F-50CC-4647-A13F-E35264F811B6}"/>
   </bookViews>
   <sheets>
     <sheet name="Student_Performance_2026" sheetId="1" r:id="rId1"/>
@@ -19,20 +19,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Cleaned_Data!$A$1:$L$546</definedName>
-    <definedName name="_xlchart.v1.0" hidden="1">Cleaned_Data!$E$2:$E$546</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Cleaned_Data!$M$2:$M$546</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">Cleaned_Data!$I$2:$I$546</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">Cleaned_Data!$I$2:$I$546</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">(Cleaned_Data!$Q$2,Cleaned_Data!$R$2,Cleaned_Data!$S$2,Cleaned_Data!$T$2,Cleaned_Data!$U$2)</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">Cleaned_Data!$M$2:$M$546</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Cleaned_Data!$F$1</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Cleaned_Data!$F$2:$F$557</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Cleaned_Data!$J$1</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Cleaned_Data!$J$2:$J$557</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Cleaned_Data!$L$1</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Cleaned_Data!$L$2:$L$557</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Cleaned_Data!$M$2:$M$546</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">Cleaned_Data!$M$2:$M$546</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">Cleaned_Data!$M$2:$M$546</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Cleaned_Data!$I$2:$I$546</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2236" uniqueCount="587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2234" uniqueCount="587">
   <si>
     <t>student_ID</t>
   </si>
@@ -2323,16 +2311,15 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -7728,9 +7715,12 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx2"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -7757,9 +7747,12 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx2"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -7772,8 +7765,9 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:view3D>
-      <c:rotX val="75"/>
+      <c:rotX val="30"/>
       <c:rotY val="0"/>
+      <c:depthPercent val="100"/>
       <c:rAngAx val="0"/>
     </c:view3D>
     <c:floor>
@@ -7830,37 +7824,27 @@
             <c:idx val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:gradFill rotWithShape="1">
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent1">
-                      <a:satMod val="103000"/>
-                      <a:lumMod val="102000"/>
-                      <a:tint val="94000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="50000">
-                    <a:schemeClr val="accent1">
-                      <a:satMod val="110000"/>
-                      <a:lumMod val="100000"/>
-                      <a:shade val="100000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent1">
-                      <a:lumMod val="99000"/>
-                      <a:satMod val="120000"/>
-                      <a:shade val="78000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="0"/>
-              </a:gradFill>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
               <a:ln>
                 <a:noFill/>
               </a:ln>
-              <a:effectLst/>
-              <a:sp3d/>
+              <a:effectLst>
+                <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="10000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="127000" h="127000"/>
+                <a:bevelB w="127000" h="127000"/>
+              </a:sp3d>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -7872,37 +7856,27 @@
             <c:idx val="1"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:gradFill rotWithShape="1">
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent2">
-                      <a:satMod val="103000"/>
-                      <a:lumMod val="102000"/>
-                      <a:tint val="94000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="50000">
-                    <a:schemeClr val="accent2">
-                      <a:satMod val="110000"/>
-                      <a:lumMod val="100000"/>
-                      <a:shade val="100000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent2">
-                      <a:lumMod val="99000"/>
-                      <a:satMod val="120000"/>
-                      <a:shade val="78000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="0"/>
-              </a:gradFill>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
               <a:ln>
                 <a:noFill/>
               </a:ln>
-              <a:effectLst/>
-              <a:sp3d/>
+              <a:effectLst>
+                <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="10000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="127000" h="127000"/>
+                <a:bevelB w="127000" h="127000"/>
+              </a:sp3d>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -7914,37 +7888,27 @@
             <c:idx val="2"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:gradFill rotWithShape="1">
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent3">
-                      <a:satMod val="103000"/>
-                      <a:lumMod val="102000"/>
-                      <a:tint val="94000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="50000">
-                    <a:schemeClr val="accent3">
-                      <a:satMod val="110000"/>
-                      <a:lumMod val="100000"/>
-                      <a:shade val="100000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent3">
-                      <a:lumMod val="99000"/>
-                      <a:satMod val="120000"/>
-                      <a:shade val="78000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="0"/>
-              </a:gradFill>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
               <a:ln>
                 <a:noFill/>
               </a:ln>
-              <a:effectLst/>
-              <a:sp3d/>
+              <a:effectLst>
+                <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="10000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="127000" h="127000"/>
+                <a:bevelB w="127000" h="127000"/>
+              </a:sp3d>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -7956,37 +7920,27 @@
             <c:idx val="3"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:gradFill rotWithShape="1">
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent4">
-                      <a:satMod val="103000"/>
-                      <a:lumMod val="102000"/>
-                      <a:tint val="94000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="50000">
-                    <a:schemeClr val="accent4">
-                      <a:satMod val="110000"/>
-                      <a:lumMod val="100000"/>
-                      <a:shade val="100000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent4">
-                      <a:lumMod val="99000"/>
-                      <a:satMod val="120000"/>
-                      <a:shade val="78000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="0"/>
-              </a:gradFill>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
               <a:ln>
                 <a:noFill/>
               </a:ln>
-              <a:effectLst/>
-              <a:sp3d/>
+              <a:effectLst>
+                <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="10000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="127000" h="127000"/>
+                <a:bevelB w="127000" h="127000"/>
+              </a:sp3d>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -7998,37 +7952,27 @@
             <c:idx val="4"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:gradFill rotWithShape="1">
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent5">
-                      <a:satMod val="103000"/>
-                      <a:lumMod val="102000"/>
-                      <a:tint val="94000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="50000">
-                    <a:schemeClr val="accent5">
-                      <a:satMod val="110000"/>
-                      <a:lumMod val="100000"/>
-                      <a:shade val="100000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent5">
-                      <a:lumMod val="99000"/>
-                      <a:satMod val="120000"/>
-                      <a:shade val="78000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="0"/>
-              </a:gradFill>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
               <a:ln>
                 <a:noFill/>
               </a:ln>
-              <a:effectLst/>
-              <a:sp3d/>
+              <a:effectLst>
+                <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="10000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="127000" h="127000"/>
+                <a:bevelB w="127000" h="127000"/>
+              </a:sp3d>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -8037,8 +7981,243 @@
             </c:extLst>
           </c:dPt>
           <c:dLbls>
-            <c:delete val="1"/>
-            <c:extLst/>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-9558-3F48-B080-D5B120AF4DFC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="accent2"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-9558-3F48-B080-D5B120AF4DFC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="accent3"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-9558-3F48-B080-D5B120AF4DFC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="accent4"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-9558-3F48-B080-D5B120AF4DFC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="accent5"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000009-9558-3F48-B080-D5B120AF4DFC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
           </c:dLbls>
           <c:val>
             <c:numRef>
@@ -8071,7 +8250,7 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="ctr"/>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -8089,34 +8268,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr rtl="0">
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx2"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -8134,7 +8285,7 @@
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx2">
+        <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
           <a:lumOff val="85000"/>
         </a:schemeClr>
@@ -11908,7 +12059,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.11</cx:f>
+        <cx:f>_xlchart.v1.1</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -11969,7 +12120,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.13</cx:f>
+        <cx:f>_xlchart.v1.0</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -12742,27 +12893,45 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="255">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="259">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx2">
+          <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -12770,48 +12939,25 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <cs:styleClr val="auto"/>
     </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0"/>
   </cs:dataLabel>
   <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk2">
-        <a:lumMod val="75000"/>
-      </a:schemeClr>
+      <cs:styleClr val="auto"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -12819,49 +12965,78 @@
       </a:solidFill>
       <a:ln>
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" b="1" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
       <a:spAutoFit/>
     </cs:bodyPr>
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="2"/>
+    <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="63500" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="2"/>
+    <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="10000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+      <a:scene3d>
+        <a:camera prst="orthographicFront"/>
+        <a:lightRig rig="threePt" dir="t"/>
+      </a:scene3d>
+      <a:sp3d>
+        <a:bevelT w="127000" h="127000"/>
+        <a:bevelB w="127000" h="127000"/>
+      </a:sp3d>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="2"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="31750" cap="rnd">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -12871,19 +13046,21 @@
   </cs:dataPointLine>
   <cs:dataPointMarker>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="2"/>
+    <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="12700">
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="lt2"/>
+          <a:schemeClr val="lt1"/>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
@@ -12892,10 +13069,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="2"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -12911,16 +13088,21 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx2">
+          <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -12930,22 +13112,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -12954,17 +13137,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:prstDash val="dash"/>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -12973,13 +13156,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="75000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -12991,20 +13175,26 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx2">
+          <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -13018,16 +13208,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx2">
+          <a:schemeClr val="tx1">
             <a:lumMod val="5000"/>
             <a:lumOff val="95000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -13036,17 +13227,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:prstDash val="dash"/>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
@@ -13055,16 +13246,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx2">
+          <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -13073,24 +13265,27 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -13098,19 +13293,11 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -13118,17 +13305,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:prstDash val="dash"/>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:seriesLine>
@@ -13137,9 +13324,12 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200"/>
+    <cs:defRPr sz="1600" b="1" kern="1200" cap="all" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -13148,7 +13338,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
@@ -13164,7 +13354,10 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:trendlineLabel>
@@ -13173,19 +13366,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -13194,7 +13388,10 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
@@ -13203,8 +13400,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -14745,16 +14948,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>558800</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -14783,15 +14986,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>215900</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>787400</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -14821,15 +15024,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>146756</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -14859,15 +15062,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>622300</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>241300</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>45156</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -14937,15 +15140,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>121356</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -15333,7 +15536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4B235CE-050B-7C41-B57B-600A6E977AB9}">
-  <dimension ref="A1:M553"/>
+  <dimension ref="A1:M551"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
@@ -23776,6 +23979,10 @@
       <c r="A223" t="s">
         <v>586</v>
       </c>
+      <c r="F223" t="str">
+        <f>TRIM(A2)</f>
+        <v>S011</v>
+      </c>
     </row>
     <row r="224" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
@@ -35881,345 +36088,307 @@
         <v>6.19</v>
       </c>
     </row>
+    <row r="544" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A544" t="s">
+        <v>553</v>
+      </c>
+      <c r="B544">
+        <v>25</v>
+      </c>
+      <c r="C544" t="s">
+        <v>13</v>
+      </c>
+      <c r="D544">
+        <v>7.8</v>
+      </c>
+      <c r="E544">
+        <v>3.1</v>
+      </c>
+      <c r="G544">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H544">
+        <v>1.6</v>
+      </c>
+      <c r="I544">
+        <v>6.6</v>
+      </c>
+      <c r="J544">
+        <v>74</v>
+      </c>
+      <c r="K544">
+        <v>2.5</v>
+      </c>
+      <c r="L544">
+        <v>7.2</v>
+      </c>
+      <c r="M544">
+        <v>7.4</v>
+      </c>
+    </row>
     <row r="545" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B545">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C545" t="s">
         <v>13</v>
       </c>
       <c r="D545">
-        <v>7.8</v>
+        <v>5.6</v>
       </c>
       <c r="E545">
-        <v>3.1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="G545">
-        <v>2.2000000000000002</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="H545">
-        <v>1.6</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I545">
-        <v>6.6</v>
+        <v>7.9</v>
       </c>
       <c r="J545">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="K545">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="L545">
-        <v>7.2</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="M545">
-        <v>7.4</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="546" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B546">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C546" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D546">
-        <v>5.6</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="E546">
-        <v>2.2000000000000002</v>
+        <v>1.6</v>
       </c>
       <c r="G546">
-        <v>4.4000000000000004</v>
+        <v>5.9</v>
       </c>
       <c r="H546">
-        <v>1.1000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="I546">
-        <v>7.9</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="J546">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="K546">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="L546">
-        <v>8.4700000000000006</v>
+        <v>7.63</v>
       </c>
       <c r="M546">
-        <v>8.67</v>
+        <v>7.83</v>
       </c>
     </row>
     <row r="547" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B547">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C547" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D547">
-        <v>4.0999999999999996</v>
+        <v>6.4</v>
       </c>
       <c r="E547">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="G547">
-        <v>5.9</v>
+        <v>3.6</v>
       </c>
       <c r="H547">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="I547">
-        <v>8.1999999999999993</v>
+        <v>7.5</v>
       </c>
       <c r="J547">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K547">
         <v>2.6</v>
       </c>
       <c r="L547">
-        <v>7.63</v>
+        <v>7.74</v>
       </c>
       <c r="M547">
-        <v>7.83</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="548" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B548">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C548" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D548">
-        <v>6.4</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="E548">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="G548">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="H548">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="I548">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="J548">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="K548">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="L548">
-        <v>7.74</v>
+        <v>5.62</v>
       </c>
       <c r="M548">
-        <v>7.94</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="549" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B549">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C549" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D549">
-        <v>8.3000000000000007</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="E549">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="G549">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="H549">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="I549">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="J549">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="K549">
-        <v>1.9</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="L549">
-        <v>5.62</v>
+        <v>6.29</v>
       </c>
       <c r="M549">
-        <v>5.82</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="550" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B550">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C550" t="s">
         <v>13</v>
       </c>
       <c r="D550">
-        <v>9.8000000000000007</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="E550">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="G550">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="H550">
+        <v>1.7</v>
+      </c>
+      <c r="I550">
+        <v>5.8</v>
+      </c>
+      <c r="J550">
+        <v>59</v>
+      </c>
+      <c r="K550">
         <v>2</v>
       </c>
-      <c r="I550">
-        <v>6.3</v>
-      </c>
-      <c r="J550">
-        <v>64</v>
-      </c>
-      <c r="K550">
-        <v>2.2000000000000002</v>
-      </c>
       <c r="L550">
-        <v>6.29</v>
+        <v>5.79</v>
       </c>
       <c r="M550">
-        <v>6.49</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="551" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>559</v>
+        <v>582</v>
       </c>
       <c r="B551">
-        <v>24</v>
-      </c>
-      <c r="C551" t="s">
-        <v>13</v>
+        <v>0</v>
+      </c>
+      <c r="C551">
+        <v>34</v>
       </c>
       <c r="D551">
-        <v>8.6999999999999993</v>
+        <v>43</v>
       </c>
       <c r="E551">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="G551">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="H551">
-        <v>1.7</v>
+        <v>657</v>
       </c>
       <c r="I551">
-        <v>5.8</v>
-      </c>
-      <c r="J551">
-        <v>59</v>
+        <v>54</v>
+      </c>
+      <c r="J551" t="s">
+        <v>583</v>
       </c>
       <c r="K551">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="L551">
-        <v>5.79</v>
+        <v>23</v>
       </c>
       <c r="M551">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="552" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A552" t="s">
-        <v>173</v>
-      </c>
-      <c r="B552">
-        <v>22</v>
-      </c>
-      <c r="C552" t="s">
-        <v>13</v>
-      </c>
-      <c r="D552">
-        <v>8.4</v>
-      </c>
-      <c r="E552">
-        <v>3.4</v>
-      </c>
-      <c r="G552">
-        <v>1.6</v>
-      </c>
-      <c r="H552">
-        <v>1.7</v>
-      </c>
-      <c r="I552">
-        <v>5.3</v>
-      </c>
-      <c r="J552">
-        <v>60</v>
-      </c>
-      <c r="K552">
-        <v>2</v>
-      </c>
-      <c r="L552">
-        <v>5.89</v>
-      </c>
-      <c r="M552">
-        <v>6.09</v>
-      </c>
-    </row>
-    <row r="553" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A553" t="s">
-        <v>582</v>
-      </c>
-      <c r="B553">
-        <v>0</v>
-      </c>
-      <c r="C553">
-        <v>34</v>
-      </c>
-      <c r="D553">
-        <v>43</v>
-      </c>
-      <c r="E553">
-        <v>3.3</v>
-      </c>
-      <c r="G553">
-        <v>6</v>
-      </c>
-      <c r="H553">
-        <v>657</v>
-      </c>
-      <c r="I553">
-        <v>54</v>
-      </c>
-      <c r="J553" t="s">
-        <v>583</v>
-      </c>
-      <c r="K553">
-        <v>43</v>
-      </c>
-      <c r="L553">
-        <v>23</v>
-      </c>
-      <c r="M553">
         <v>23</v>
       </c>
     </row>
@@ -36230,7 +36399,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAE3D4AB-79CA-884A-9A5E-1A19FCA51F34}">
-  <dimension ref="A1:Z546"/>
+  <dimension ref="A1:Z547"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -36297,7 +36466,7 @@
       <c r="M1" s="5" t="s">
         <v>579</v>
       </c>
-      <c r="O1" s="6"/>
+      <c r="O1" s="2"/>
       <c r="P1" s="5" t="s">
         <v>1</v>
       </c>
@@ -36367,7 +36536,7 @@
         <v>7.92</v>
       </c>
       <c r="M2">
-        <f>F2+J2</f>
+        <f t="shared" ref="M2:M65" si="0">F2+J2</f>
         <v>7.6999999999999993</v>
       </c>
       <c r="O2" s="2" t="s">
@@ -36443,7 +36612,7 @@
         <v>6.87</v>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:M66" si="0">F3+J3</f>
+        <f t="shared" si="0"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="O3" s="2" t="s">
@@ -39331,7 +39500,7 @@
         <v>9.51</v>
       </c>
       <c r="M66">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="M66:M129" si="1">F66+J66</f>
         <v>9</v>
       </c>
     </row>
@@ -39373,7 +39542,7 @@
         <v>7.36</v>
       </c>
       <c r="M67">
-        <f t="shared" ref="M67:M130" si="1">F67+J67</f>
+        <f t="shared" si="1"/>
         <v>6.4</v>
       </c>
     </row>
@@ -42019,7 +42188,7 @@
         <v>8.85</v>
       </c>
       <c r="M130">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="M130:M193" si="2">F130+J130</f>
         <v>8.4</v>
       </c>
     </row>
@@ -42061,7 +42230,7 @@
         <v>6.25</v>
       </c>
       <c r="M131">
-        <f t="shared" ref="M131:M194" si="2">F131+J131</f>
+        <f t="shared" si="2"/>
         <v>2.7</v>
       </c>
     </row>
@@ -44707,7 +44876,7 @@
         <v>8.8800000000000008</v>
       </c>
       <c r="M194">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="M194:M257" si="3">F194+J194</f>
         <v>7.9</v>
       </c>
     </row>
@@ -44749,7 +44918,7 @@
         <v>6.4</v>
       </c>
       <c r="M195">
-        <f t="shared" ref="M195:M258" si="3">F195+J195</f>
+        <f t="shared" si="3"/>
         <v>4.0999999999999996</v>
       </c>
     </row>
@@ -47395,7 +47564,7 @@
         <v>8.64</v>
       </c>
       <c r="M258">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="M258:M321" si="4">F258+J258</f>
         <v>7.6</v>
       </c>
     </row>
@@ -47437,7 +47606,7 @@
         <v>6.04</v>
       </c>
       <c r="M259">
-        <f t="shared" ref="M259:M273" si="4">F259+J259</f>
+        <f t="shared" si="4"/>
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -48067,7 +48236,7 @@
         <v>8.16</v>
       </c>
       <c r="M274">
-        <f>F274+J274</f>
+        <f t="shared" si="4"/>
         <v>7.4</v>
       </c>
     </row>
@@ -48109,7 +48278,7 @@
         <v>8.1</v>
       </c>
       <c r="M275">
-        <f t="shared" ref="M275:M338" si="5">F275+J275</f>
+        <f t="shared" si="4"/>
         <v>8.5</v>
       </c>
     </row>
@@ -48151,7 +48320,7 @@
         <v>7.84</v>
       </c>
       <c r="M276">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>4.8000000000000007</v>
       </c>
     </row>
@@ -48193,7 +48362,7 @@
         <v>6.95</v>
       </c>
       <c r="M277">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5.0999999999999996</v>
       </c>
     </row>
@@ -48235,7 +48404,7 @@
         <v>5.71</v>
       </c>
       <c r="M278">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3.5</v>
       </c>
     </row>
@@ -48277,7 +48446,7 @@
         <v>7.84</v>
       </c>
       <c r="M279">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5.9</v>
       </c>
     </row>
@@ -48319,7 +48488,7 @@
         <v>5.99</v>
       </c>
       <c r="M280">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2.1</v>
       </c>
     </row>
@@ -48361,7 +48530,7 @@
         <v>6.24</v>
       </c>
       <c r="M281">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2.9000000000000004</v>
       </c>
     </row>
@@ -48403,7 +48572,7 @@
         <v>6.28</v>
       </c>
       <c r="M282">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2.6</v>
       </c>
     </row>
@@ -48445,7 +48614,7 @@
         <v>9.1199999999999992</v>
       </c>
       <c r="M283">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>8.4</v>
       </c>
     </row>
@@ -48487,7 +48656,7 @@
         <v>7.84</v>
       </c>
       <c r="M284">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>6.2</v>
       </c>
     </row>
@@ -48529,7 +48698,7 @@
         <v>7.19</v>
       </c>
       <c r="M285">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
     </row>
@@ -48571,7 +48740,7 @@
         <v>5.91</v>
       </c>
       <c r="M286">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2.7</v>
       </c>
     </row>
@@ -48613,7 +48782,7 @@
         <v>6.81</v>
       </c>
       <c r="M287">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
     </row>
@@ -48655,7 +48824,7 @@
         <v>6.01</v>
       </c>
       <c r="M288">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3.8</v>
       </c>
     </row>
@@ -48697,7 +48866,7 @@
         <v>7.95</v>
       </c>
       <c r="M289">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>7.1999999999999993</v>
       </c>
     </row>
@@ -48739,7 +48908,7 @@
         <v>7.45</v>
       </c>
       <c r="M290">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5.5</v>
       </c>
     </row>
@@ -48781,7 +48950,7 @@
         <v>8.48</v>
       </c>
       <c r="M291">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>8.6</v>
       </c>
     </row>
@@ -48823,7 +48992,7 @@
         <v>7.53</v>
       </c>
       <c r="M292">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5.3</v>
       </c>
     </row>
@@ -48865,7 +49034,7 @@
         <v>5.52</v>
       </c>
       <c r="M293">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2.1</v>
       </c>
     </row>
@@ -48907,7 +49076,7 @@
         <v>6.35</v>
       </c>
       <c r="M294">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2.4</v>
       </c>
     </row>
@@ -48949,7 +49118,7 @@
         <v>6.92</v>
       </c>
       <c r="M295">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>6.1999999999999993</v>
       </c>
     </row>
@@ -48991,7 +49160,7 @@
         <v>9.41</v>
       </c>
       <c r="M296">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>7.3000000000000007</v>
       </c>
     </row>
@@ -49033,7 +49202,7 @@
         <v>5.85</v>
       </c>
       <c r="M297">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3.7</v>
       </c>
     </row>
@@ -49075,7 +49244,7 @@
         <v>6.54</v>
       </c>
       <c r="M298">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
     </row>
@@ -49117,7 +49286,7 @@
         <v>9.64</v>
       </c>
       <c r="M299">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>8.1000000000000014</v>
       </c>
     </row>
@@ -49159,7 +49328,7 @@
         <v>6.85</v>
       </c>
       <c r="M300">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
     </row>
@@ -49201,7 +49370,7 @@
         <v>7.51</v>
       </c>
       <c r="M301">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5.4</v>
       </c>
     </row>
@@ -49243,7 +49412,7 @@
         <v>7.89</v>
       </c>
       <c r="M302">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>6.4</v>
       </c>
     </row>
@@ -49285,7 +49454,7 @@
         <v>9.4499999999999993</v>
       </c>
       <c r="M303">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>7.6000000000000005</v>
       </c>
     </row>
@@ -49327,7 +49496,7 @@
         <v>5.69</v>
       </c>
       <c r="M304">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3.3</v>
       </c>
     </row>
@@ -49369,7 +49538,7 @@
         <v>6.11</v>
       </c>
       <c r="M305">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2.8</v>
       </c>
     </row>
@@ -49411,7 +49580,7 @@
         <v>8.2100000000000009</v>
       </c>
       <c r="M306">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>7.3</v>
       </c>
     </row>
@@ -49453,7 +49622,7 @@
         <v>8.35</v>
       </c>
       <c r="M307">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>7.8999999999999995</v>
       </c>
     </row>
@@ -49495,7 +49664,7 @@
         <v>7.66</v>
       </c>
       <c r="M308">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
     </row>
@@ -49537,7 +49706,7 @@
         <v>6.28</v>
       </c>
       <c r="M309">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3.2</v>
       </c>
     </row>
@@ -49579,7 +49748,7 @@
         <v>7.51</v>
       </c>
       <c r="M310">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>4.5999999999999996</v>
       </c>
     </row>
@@ -49621,7 +49790,7 @@
         <v>7.33</v>
       </c>
       <c r="M311">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>4.6999999999999993</v>
       </c>
     </row>
@@ -49663,7 +49832,7 @@
         <v>6.35</v>
       </c>
       <c r="M312">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2.8</v>
       </c>
     </row>
@@ -49705,7 +49874,7 @@
         <v>6.79</v>
       </c>
       <c r="M313">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>4.3</v>
       </c>
     </row>
@@ -49747,7 +49916,7 @@
         <v>7.2</v>
       </c>
       <c r="M314">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5.6999999999999993</v>
       </c>
     </row>
@@ -49789,7 +49958,7 @@
         <v>9.18</v>
       </c>
       <c r="M315">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
     </row>
@@ -49831,7 +50000,7 @@
         <v>5.95</v>
       </c>
       <c r="M316">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3.5</v>
       </c>
     </row>
@@ -49873,7 +50042,7 @@
         <v>6.94</v>
       </c>
       <c r="M317">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
     </row>
@@ -49915,7 +50084,7 @@
         <v>6.2</v>
       </c>
       <c r="M318">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2.5</v>
       </c>
     </row>
@@ -49957,7 +50126,7 @@
         <v>9.3800000000000008</v>
       </c>
       <c r="M319">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>7.6</v>
       </c>
     </row>
@@ -49999,7 +50168,7 @@
         <v>5.55</v>
       </c>
       <c r="M320">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3.5</v>
       </c>
     </row>
@@ -50041,7 +50210,7 @@
         <v>9.67</v>
       </c>
       <c r="M321">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>8.6999999999999993</v>
       </c>
     </row>
@@ -50083,7 +50252,7 @@
         <v>7.52</v>
       </c>
       <c r="M322">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="M322:M385" si="5">F322+J322</f>
         <v>5.8</v>
       </c>
     </row>
@@ -50797,7 +50966,7 @@
         <v>5.75</v>
       </c>
       <c r="M339">
-        <f t="shared" ref="M339:M374" si="6">F339+J339</f>
+        <f t="shared" si="5"/>
         <v>3.8</v>
       </c>
     </row>
@@ -50839,7 +51008,7 @@
         <v>6.54</v>
       </c>
       <c r="M340">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2.3000000000000003</v>
       </c>
     </row>
@@ -50881,7 +51050,7 @@
         <v>9.09</v>
       </c>
       <c r="M341">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.4</v>
       </c>
     </row>
@@ -50923,7 +51092,7 @@
         <v>9.5299999999999994</v>
       </c>
       <c r="M342">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>8.4</v>
       </c>
     </row>
@@ -50965,7 +51134,7 @@
         <v>7.27</v>
       </c>
       <c r="M343">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>6.1</v>
       </c>
     </row>
@@ -51007,7 +51176,7 @@
         <v>9.1199999999999992</v>
       </c>
       <c r="M344">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>8.4</v>
       </c>
     </row>
@@ -51049,7 +51218,7 @@
         <v>5.83</v>
       </c>
       <c r="M345">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2.2999999999999998</v>
       </c>
     </row>
@@ -51091,7 +51260,7 @@
         <v>6.33</v>
       </c>
       <c r="M346">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2.7</v>
       </c>
     </row>
@@ -51133,7 +51302,7 @@
         <v>9.27</v>
       </c>
       <c r="M347">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>8.1999999999999993</v>
       </c>
     </row>
@@ -51175,7 +51344,7 @@
         <v>9.2899999999999991</v>
       </c>
       <c r="M348">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>8.9</v>
       </c>
     </row>
@@ -51217,7 +51386,7 @@
         <v>9.7100000000000009</v>
       </c>
       <c r="M349">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>9.1000000000000014</v>
       </c>
     </row>
@@ -51259,7 +51428,7 @@
         <v>6.73</v>
       </c>
       <c r="M350">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2.4000000000000004</v>
       </c>
     </row>
@@ -51301,7 +51470,7 @@
         <v>6.49</v>
       </c>
       <c r="M351">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>4.2</v>
       </c>
     </row>
@@ -51343,7 +51512,7 @@
         <v>5.8</v>
       </c>
       <c r="M352">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>3.2</v>
       </c>
     </row>
@@ -51385,7 +51554,7 @@
         <v>8.32</v>
       </c>
       <c r="M353">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.3</v>
       </c>
     </row>
@@ -51427,7 +51596,7 @@
         <v>5.92</v>
       </c>
       <c r="M354">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2.6</v>
       </c>
     </row>
@@ -51469,7 +51638,7 @@
         <v>7.9</v>
       </c>
       <c r="M355">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>5.7</v>
       </c>
     </row>
@@ -51511,7 +51680,7 @@
         <v>6.91</v>
       </c>
       <c r="M356">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>4.6999999999999993</v>
       </c>
     </row>
@@ -51553,7 +51722,7 @@
         <v>5.81</v>
       </c>
       <c r="M357">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2.1999999999999997</v>
       </c>
     </row>
@@ -51595,7 +51764,7 @@
         <v>6.37</v>
       </c>
       <c r="M358">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2.1</v>
       </c>
     </row>
@@ -51637,7 +51806,7 @@
         <v>5.83</v>
       </c>
       <c r="M359">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2.4</v>
       </c>
     </row>
@@ -51679,7 +51848,7 @@
         <v>6.51</v>
       </c>
       <c r="M360">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>3.8000000000000003</v>
       </c>
     </row>
@@ -51721,7 +51890,7 @@
         <v>8.8800000000000008</v>
       </c>
       <c r="M361">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.4</v>
       </c>
     </row>
@@ -51763,7 +51932,7 @@
         <v>9.73</v>
       </c>
       <c r="M362">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>8.6000000000000014</v>
       </c>
     </row>
@@ -51805,7 +51974,7 @@
         <v>6.2</v>
       </c>
       <c r="M363">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>3.7</v>
       </c>
     </row>
@@ -51847,7 +52016,7 @@
         <v>8.1</v>
       </c>
       <c r="M364">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>8.1000000000000014</v>
       </c>
     </row>
@@ -51889,7 +52058,7 @@
         <v>8.92</v>
       </c>
       <c r="M365">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
     </row>
@@ -51931,7 +52100,7 @@
         <v>8.19</v>
       </c>
       <c r="M366">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
@@ -51973,7 +52142,7 @@
         <v>6.56</v>
       </c>
       <c r="M367">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>3.7</v>
       </c>
     </row>
@@ -52015,7 +52184,7 @@
         <v>6.22</v>
       </c>
       <c r="M368">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>3.4000000000000004</v>
       </c>
     </row>
@@ -52057,7 +52226,7 @@
         <v>5.76</v>
       </c>
       <c r="M369">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>3.4</v>
       </c>
     </row>
@@ -52099,7 +52268,7 @@
         <v>6.59</v>
       </c>
       <c r="M370">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>3.7</v>
       </c>
     </row>
@@ -52141,7 +52310,7 @@
         <v>7.34</v>
       </c>
       <c r="M371">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>6.1999999999999993</v>
       </c>
     </row>
@@ -52183,7 +52352,7 @@
         <v>9.1300000000000008</v>
       </c>
       <c r="M372">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>8.1999999999999993</v>
       </c>
     </row>
@@ -52225,7 +52394,7 @@
         <v>7.23</v>
       </c>
       <c r="M373">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>4.6999999999999993</v>
       </c>
     </row>
@@ -52267,7 +52436,7 @@
         <v>6.16</v>
       </c>
       <c r="M374">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2.9000000000000004</v>
       </c>
     </row>
@@ -52309,7 +52478,7 @@
         <v>7.52</v>
       </c>
       <c r="M375">
-        <f>F375+J375</f>
+        <f t="shared" si="5"/>
         <v>5.0999999999999996</v>
       </c>
     </row>
@@ -52351,7 +52520,7 @@
         <v>8.44</v>
       </c>
       <c r="M376">
-        <f t="shared" ref="M376:M439" si="7">F376+J376</f>
+        <f t="shared" si="5"/>
         <v>8.6999999999999993</v>
       </c>
     </row>
@@ -52393,7 +52562,7 @@
         <v>7.74</v>
       </c>
       <c r="M377">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>6.6</v>
       </c>
     </row>
@@ -52435,7 +52604,7 @@
         <v>6.95</v>
       </c>
       <c r="M378">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>6.1</v>
       </c>
     </row>
@@ -52477,7 +52646,7 @@
         <v>9</v>
       </c>
       <c r="M379">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>7.7</v>
       </c>
     </row>
@@ -52519,7 +52688,7 @@
         <v>9.08</v>
       </c>
       <c r="M380">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
     </row>
@@ -52561,7 +52730,7 @@
         <v>5.76</v>
       </c>
       <c r="M381">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>2.1999999999999997</v>
       </c>
     </row>
@@ -52603,7 +52772,7 @@
         <v>7.85</v>
       </c>
       <c r="M382">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>8.4</v>
       </c>
     </row>
@@ -52645,7 +52814,7 @@
         <v>9.68</v>
       </c>
       <c r="M383">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>7.4</v>
       </c>
     </row>
@@ -52687,7 +52856,7 @@
         <v>5.74</v>
       </c>
       <c r="M384">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>2.8</v>
       </c>
     </row>
@@ -52729,7 +52898,7 @@
         <v>7.96</v>
       </c>
       <c r="M385">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>7.9</v>
       </c>
     </row>
@@ -52771,7 +52940,7 @@
         <v>5.51</v>
       </c>
       <c r="M386">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="M386:M449" si="6">F386+J386</f>
         <v>3.1</v>
       </c>
     </row>
@@ -52813,7 +52982,7 @@
         <v>6.82</v>
       </c>
       <c r="M387">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>5.5</v>
       </c>
     </row>
@@ -52855,7 +53024,7 @@
         <v>8.35</v>
       </c>
       <c r="M388">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>7.1</v>
       </c>
     </row>
@@ -52897,7 +53066,7 @@
         <v>7.73</v>
       </c>
       <c r="M389">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>5.9</v>
       </c>
     </row>
@@ -52939,7 +53108,7 @@
         <v>9.61</v>
       </c>
       <c r="M390">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>8.8000000000000007</v>
       </c>
     </row>
@@ -52981,7 +53150,7 @@
         <v>5.61</v>
       </c>
       <c r="M391">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>3.3</v>
       </c>
     </row>
@@ -53023,7 +53192,7 @@
         <v>7.92</v>
       </c>
       <c r="M392">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>5.2</v>
       </c>
     </row>
@@ -53065,7 +53234,7 @@
         <v>5.83</v>
       </c>
       <c r="M393">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
     </row>
@@ -53107,7 +53276,7 @@
         <v>7.17</v>
       </c>
       <c r="M394">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>6.4</v>
       </c>
     </row>
@@ -53149,7 +53318,7 @@
         <v>8.25</v>
       </c>
       <c r="M395">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>7.8999999999999995</v>
       </c>
     </row>
@@ -53191,7 +53360,7 @@
         <v>7.98</v>
       </c>
       <c r="M396">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>5.4</v>
       </c>
     </row>
@@ -53233,7 +53402,7 @@
         <v>6.21</v>
       </c>
       <c r="M397">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>3.9000000000000004</v>
       </c>
     </row>
@@ -53275,7 +53444,7 @@
         <v>6.97</v>
       </c>
       <c r="M398">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>5.6999999999999993</v>
       </c>
     </row>
@@ -53317,7 +53486,7 @@
         <v>7.29</v>
       </c>
       <c r="M399">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>5.6</v>
       </c>
     </row>
@@ -53359,7 +53528,7 @@
         <v>7.77</v>
       </c>
       <c r="M400">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>5.5</v>
       </c>
     </row>
@@ -53401,7 +53570,7 @@
         <v>7.85</v>
       </c>
       <c r="M401">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>6.6</v>
       </c>
     </row>
@@ -53443,7 +53612,7 @@
         <v>8.0500000000000007</v>
       </c>
       <c r="M402">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>8.6000000000000014</v>
       </c>
     </row>
@@ -53485,7 +53654,7 @@
         <v>6.5</v>
       </c>
       <c r="M403">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>2.3000000000000003</v>
       </c>
     </row>
@@ -53527,7 +53696,7 @@
         <v>7.14</v>
       </c>
       <c r="M404">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>6.3</v>
       </c>
     </row>
@@ -53569,7 +53738,7 @@
         <v>7.79</v>
       </c>
       <c r="M405">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>4.7</v>
       </c>
     </row>
@@ -53611,7 +53780,7 @@
         <v>8.17</v>
       </c>
       <c r="M406">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>7.5</v>
       </c>
     </row>
@@ -53653,7 +53822,7 @@
         <v>7.76</v>
       </c>
       <c r="M407">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>4.8000000000000007</v>
       </c>
     </row>
@@ -53695,7 +53864,7 @@
         <v>7.47</v>
       </c>
       <c r="M408">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>5.8</v>
       </c>
     </row>
@@ -53737,7 +53906,7 @@
         <v>9.77</v>
       </c>
       <c r="M409">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>7.6</v>
       </c>
     </row>
@@ -53779,7 +53948,7 @@
         <v>7.68</v>
       </c>
       <c r="M410">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>6.4</v>
       </c>
     </row>
@@ -53821,7 +53990,7 @@
         <v>6.9</v>
       </c>
       <c r="M411">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>4.5999999999999996</v>
       </c>
     </row>
@@ -53863,7 +54032,7 @@
         <v>6.95</v>
       </c>
       <c r="M412">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>5.4</v>
       </c>
     </row>
@@ -53905,7 +54074,7 @@
         <v>6.06</v>
       </c>
       <c r="M413">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>2.7</v>
       </c>
     </row>
@@ -53947,7 +54116,7 @@
         <v>7.66</v>
       </c>
       <c r="M414">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>5.4</v>
       </c>
     </row>
@@ -53989,7 +54158,7 @@
         <v>7.16</v>
       </c>
       <c r="M415">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>6.4</v>
       </c>
     </row>
@@ -54031,7 +54200,7 @@
         <v>8.74</v>
       </c>
       <c r="M416">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
     </row>
@@ -54073,7 +54242,7 @@
         <v>7.79</v>
       </c>
       <c r="M417">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>5.6</v>
       </c>
     </row>
@@ -54115,7 +54284,7 @@
         <v>5.63</v>
       </c>
       <c r="M418">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>2.9</v>
       </c>
     </row>
@@ -54157,7 +54326,7 @@
         <v>5.75</v>
       </c>
       <c r="M419">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>3.5</v>
       </c>
     </row>
@@ -54199,7 +54368,7 @@
         <v>6.11</v>
       </c>
       <c r="M420">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
     </row>
@@ -54241,7 +54410,7 @@
         <v>5.64</v>
       </c>
       <c r="M421">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>3.5</v>
       </c>
     </row>
@@ -54283,7 +54452,7 @@
         <v>5.8</v>
       </c>
       <c r="M422">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>2.8</v>
       </c>
     </row>
@@ -54325,7 +54494,7 @@
         <v>5.78</v>
       </c>
       <c r="M423">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>2.7</v>
       </c>
     </row>
@@ -54367,7 +54536,7 @@
         <v>9.11</v>
       </c>
       <c r="M424">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>7.2</v>
       </c>
     </row>
@@ -54409,7 +54578,7 @@
         <v>6.36</v>
       </c>
       <c r="M425">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>3.4000000000000004</v>
       </c>
     </row>
@@ -54451,7 +54620,7 @@
         <v>8.14</v>
       </c>
       <c r="M426">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>8.6999999999999993</v>
       </c>
     </row>
@@ -54493,7 +54662,7 @@
         <v>7.26</v>
       </c>
       <c r="M427">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>5.0999999999999996</v>
       </c>
     </row>
@@ -54535,7 +54704,7 @@
         <v>6.83</v>
       </c>
       <c r="M428">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>5.8</v>
       </c>
     </row>
@@ -54577,7 +54746,7 @@
         <v>6.57</v>
       </c>
       <c r="M429">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>2.4000000000000004</v>
       </c>
     </row>
@@ -54619,7 +54788,7 @@
         <v>5.9</v>
       </c>
       <c r="M430">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>3.6</v>
       </c>
     </row>
@@ -54661,7 +54830,7 @@
         <v>8.0399999999999991</v>
       </c>
       <c r="M431">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>7.4</v>
       </c>
     </row>
@@ -54703,7 +54872,7 @@
         <v>7.14</v>
       </c>
       <c r="M432">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
     </row>
@@ -54745,7 +54914,7 @@
         <v>9.2899999999999991</v>
       </c>
       <c r="M433">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>7.3000000000000007</v>
       </c>
     </row>
@@ -54787,7 +54956,7 @@
         <v>6.27</v>
       </c>
       <c r="M434">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>4.0999999999999996</v>
       </c>
     </row>
@@ -54829,7 +54998,7 @@
         <v>8.9700000000000006</v>
       </c>
       <c r="M435">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>8.8000000000000007</v>
       </c>
     </row>
@@ -54871,7 +55040,7 @@
         <v>5.83</v>
       </c>
       <c r="M436">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>3.9</v>
       </c>
     </row>
@@ -54913,7 +55082,7 @@
         <v>6.84</v>
       </c>
       <c r="M437">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>5.0999999999999996</v>
       </c>
     </row>
@@ -54955,7 +55124,7 @@
         <v>7.42</v>
       </c>
       <c r="M438">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>5.0999999999999996</v>
       </c>
     </row>
@@ -54997,7 +55166,7 @@
         <v>6.08</v>
       </c>
       <c r="M439">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>2.6</v>
       </c>
     </row>
@@ -55039,7 +55208,7 @@
         <v>6.33</v>
       </c>
       <c r="M440">
-        <f t="shared" ref="M440:M460" si="8">F440+J440</f>
+        <f t="shared" si="6"/>
         <v>3.4000000000000004</v>
       </c>
     </row>
@@ -55081,7 +55250,7 @@
         <v>7.58</v>
       </c>
       <c r="M441">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>5.6</v>
       </c>
     </row>
@@ -55123,7 +55292,7 @@
         <v>7.56</v>
       </c>
       <c r="M442">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>5.5</v>
       </c>
     </row>
@@ -55165,7 +55334,7 @@
         <v>9.01</v>
       </c>
       <c r="M443">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>8.8000000000000007</v>
       </c>
     </row>
@@ -55207,7 +55376,7 @@
         <v>7.38</v>
       </c>
       <c r="M444">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>6.5</v>
       </c>
     </row>
@@ -55249,7 +55418,7 @@
         <v>7.44</v>
       </c>
       <c r="M445">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
     </row>
@@ -55291,7 +55460,7 @@
         <v>5.87</v>
       </c>
       <c r="M446">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>2.9</v>
       </c>
     </row>
@@ -55333,7 +55502,7 @@
         <v>7.15</v>
       </c>
       <c r="M447">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>5.3</v>
       </c>
     </row>
@@ -55375,7 +55544,7 @@
         <v>9.44</v>
       </c>
       <c r="M448">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>7.4</v>
       </c>
     </row>
@@ -55417,7 +55586,7 @@
         <v>9.15</v>
       </c>
       <c r="M449">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>8.9</v>
       </c>
     </row>
@@ -55459,7 +55628,7 @@
         <v>6.65</v>
       </c>
       <c r="M450">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="M450:M513" si="7">F450+J450</f>
         <v>3.8000000000000003</v>
       </c>
     </row>
@@ -55501,7 +55670,7 @@
         <v>5.5</v>
       </c>
       <c r="M451">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>2.9000000000000004</v>
       </c>
     </row>
@@ -55543,7 +55712,7 @@
         <v>7.62</v>
       </c>
       <c r="M452">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>4.9000000000000004</v>
       </c>
     </row>
@@ -55585,7 +55754,7 @@
         <v>8.99</v>
       </c>
       <c r="M453">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>8.4</v>
       </c>
     </row>
@@ -55627,7 +55796,7 @@
         <v>8.51</v>
       </c>
       <c r="M454">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>8.3000000000000007</v>
       </c>
     </row>
@@ -55669,7 +55838,7 @@
         <v>6.81</v>
       </c>
       <c r="M455">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>4.6999999999999993</v>
       </c>
     </row>
@@ -55711,7 +55880,7 @@
         <v>8.14</v>
       </c>
       <c r="M456">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>7.8</v>
       </c>
     </row>
@@ -55753,7 +55922,7 @@
         <v>8.8699999999999992</v>
       </c>
       <c r="M457">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>8.6</v>
       </c>
     </row>
@@ -55795,7 +55964,7 @@
         <v>7.34</v>
       </c>
       <c r="M458">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>5.1999999999999993</v>
       </c>
     </row>
@@ -55837,7 +56006,7 @@
         <v>5.78</v>
       </c>
       <c r="M459">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3.0999999999999996</v>
       </c>
     </row>
@@ -55879,7 +56048,7 @@
         <v>6.4</v>
       </c>
       <c r="M460">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
@@ -55921,7 +56090,7 @@
         <v>9.3800000000000008</v>
       </c>
       <c r="M461">
-        <f>F461+J461</f>
+        <f t="shared" si="7"/>
         <v>7.3000000000000007</v>
       </c>
     </row>
@@ -55963,7 +56132,7 @@
         <v>6.69</v>
       </c>
       <c r="M462">
-        <f t="shared" ref="M462:M525" si="9">F462+J462</f>
+        <f t="shared" si="7"/>
         <v>3.1</v>
       </c>
     </row>
@@ -56005,7 +56174,7 @@
         <v>6.39</v>
       </c>
       <c r="M463">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.9000000000000004</v>
       </c>
     </row>
@@ -56047,7 +56216,7 @@
         <v>9.58</v>
       </c>
       <c r="M464">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>8.3000000000000007</v>
       </c>
     </row>
@@ -56089,7 +56258,7 @@
         <v>7.25</v>
       </c>
       <c r="M465">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>5.3</v>
       </c>
     </row>
@@ -56131,7 +56300,7 @@
         <v>6.19</v>
       </c>
       <c r="M466">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
@@ -56173,7 +56342,7 @@
         <v>8.1300000000000008</v>
       </c>
       <c r="M467">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>8.1000000000000014</v>
       </c>
     </row>
@@ -56215,7 +56384,7 @@
         <v>6.96</v>
       </c>
       <c r="M468">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>5.0999999999999996</v>
       </c>
     </row>
@@ -56257,7 +56426,7 @@
         <v>8.09</v>
       </c>
       <c r="M469">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>6.8</v>
       </c>
     </row>
@@ -56299,7 +56468,7 @@
         <v>9.7100000000000009</v>
       </c>
       <c r="M470">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>8.5</v>
       </c>
     </row>
@@ -56341,7 +56510,7 @@
         <v>6.21</v>
       </c>
       <c r="M471">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>2.1</v>
       </c>
     </row>
@@ -56383,7 +56552,7 @@
         <v>6.51</v>
       </c>
       <c r="M472">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>2.4000000000000004</v>
       </c>
     </row>
@@ -56425,7 +56594,7 @@
         <v>7.71</v>
       </c>
       <c r="M473">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>5.3000000000000007</v>
       </c>
     </row>
@@ -56467,7 +56636,7 @@
         <v>6.42</v>
       </c>
       <c r="M474">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1</v>
       </c>
     </row>
@@ -56509,7 +56678,7 @@
         <v>6.21</v>
       </c>
       <c r="M475">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1</v>
       </c>
     </row>
@@ -56551,7 +56720,7 @@
         <v>7.39</v>
       </c>
       <c r="M476">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>4.7</v>
       </c>
     </row>
@@ -56593,7 +56762,7 @@
         <v>8.4499999999999993</v>
       </c>
       <c r="M477">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
     </row>
@@ -56635,7 +56804,7 @@
         <v>6.85</v>
       </c>
       <c r="M478">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>5.9</v>
       </c>
     </row>
@@ -56677,7 +56846,7 @@
         <v>8.99</v>
       </c>
       <c r="M479">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>8.1999999999999993</v>
       </c>
     </row>
@@ -56719,7 +56888,7 @@
         <v>6.21</v>
       </c>
       <c r="M480">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.6</v>
       </c>
     </row>
@@ -56761,7 +56930,7 @@
         <v>6.73</v>
       </c>
       <c r="M481">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>2.9000000000000004</v>
       </c>
     </row>
@@ -56803,7 +56972,7 @@
         <v>7.16</v>
       </c>
       <c r="M482">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>5.4</v>
       </c>
     </row>
@@ -56845,7 +57014,7 @@
         <v>7.41</v>
       </c>
       <c r="M483">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>6.2</v>
       </c>
     </row>
@@ -56887,7 +57056,7 @@
         <v>6.09</v>
       </c>
       <c r="M484">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>2.6</v>
       </c>
     </row>
@@ -56929,7 +57098,7 @@
         <v>8</v>
       </c>
       <c r="M485">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>5.8000000000000007</v>
       </c>
     </row>
@@ -56971,7 +57140,7 @@
         <v>8.2799999999999994</v>
       </c>
       <c r="M486">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
     </row>
@@ -57013,7 +57182,7 @@
         <v>5.79</v>
       </c>
       <c r="M487">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>2.1</v>
       </c>
     </row>
@@ -57055,7 +57224,7 @@
         <v>9.5399999999999991</v>
       </c>
       <c r="M488">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
     </row>
@@ -57097,7 +57266,7 @@
         <v>8.2200000000000006</v>
       </c>
       <c r="M489">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
     </row>
@@ -57139,7 +57308,7 @@
         <v>6.58</v>
       </c>
       <c r="M490">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>4.0999999999999996</v>
       </c>
     </row>
@@ -57181,7 +57350,7 @@
         <v>7.56</v>
       </c>
       <c r="M491">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>6.4</v>
       </c>
     </row>
@@ -57223,7 +57392,7 @@
         <v>6.55</v>
       </c>
       <c r="M492">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.3000000000000003</v>
       </c>
     </row>
@@ -57265,7 +57434,7 @@
         <v>8.7799999999999994</v>
       </c>
       <c r="M493">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>8.4</v>
       </c>
     </row>
@@ -57307,7 +57476,7 @@
         <v>6.93</v>
       </c>
       <c r="M494">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>6.1999999999999993</v>
       </c>
     </row>
@@ -57349,7 +57518,7 @@
         <v>6.39</v>
       </c>
       <c r="M495">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>2.9000000000000004</v>
       </c>
     </row>
@@ -57391,7 +57560,7 @@
         <v>9.2200000000000006</v>
       </c>
       <c r="M496">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>8.1999999999999993</v>
       </c>
     </row>
@@ -57433,7 +57602,7 @@
         <v>6.71</v>
       </c>
       <c r="M497">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.4000000000000004</v>
       </c>
     </row>
@@ -57475,7 +57644,7 @@
         <v>6.21</v>
       </c>
       <c r="M498">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
@@ -57517,7 +57686,7 @@
         <v>7.71</v>
       </c>
       <c r="M499">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>6.1</v>
       </c>
     </row>
@@ -57559,7 +57728,7 @@
         <v>7.5</v>
       </c>
       <c r="M500">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>5.8</v>
       </c>
     </row>
@@ -57601,7 +57770,7 @@
         <v>7.36</v>
       </c>
       <c r="M501">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>5.3</v>
       </c>
     </row>
@@ -57643,7 +57812,7 @@
         <v>7.42</v>
       </c>
       <c r="M502">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>5.2</v>
       </c>
     </row>
@@ -57685,7 +57854,7 @@
         <v>6.99</v>
       </c>
       <c r="M503">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>5.9</v>
       </c>
     </row>
@@ -57727,7 +57896,7 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="M504">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>8.8000000000000007</v>
       </c>
     </row>
@@ -57769,7 +57938,7 @@
         <v>7.87</v>
       </c>
       <c r="M505">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
@@ -57811,7 +57980,7 @@
         <v>9.2799999999999994</v>
       </c>
       <c r="M506">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>7.6</v>
       </c>
     </row>
@@ -57853,7 +58022,7 @@
         <v>9.49</v>
       </c>
       <c r="M507">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>7.6000000000000005</v>
       </c>
     </row>
@@ -57895,7 +58064,7 @@
         <v>6.05</v>
       </c>
       <c r="M508">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>2.2999999999999998</v>
       </c>
     </row>
@@ -57937,7 +58106,7 @@
         <v>7.88</v>
       </c>
       <c r="M509">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>7.9</v>
       </c>
     </row>
@@ -57979,7 +58148,7 @@
         <v>8.1300000000000008</v>
       </c>
       <c r="M510">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>8.6999999999999993</v>
       </c>
     </row>
@@ -58021,7 +58190,7 @@
         <v>6.74</v>
       </c>
       <c r="M511">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.6</v>
       </c>
     </row>
@@ -58063,7 +58232,7 @@
         <v>6.34</v>
       </c>
       <c r="M512">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.4000000000000004</v>
       </c>
     </row>
@@ -58105,7 +58274,7 @@
         <v>7.84</v>
       </c>
       <c r="M513">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>6.3000000000000007</v>
       </c>
     </row>
@@ -58147,7 +58316,7 @@
         <v>9.52</v>
       </c>
       <c r="M514">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="M514:M546" si="8">F514+J514</f>
         <v>9.1999999999999993</v>
       </c>
     </row>
@@ -58189,7 +58358,7 @@
         <v>5.98</v>
       </c>
       <c r="M515">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>3.7</v>
       </c>
     </row>
@@ -58231,7 +58400,7 @@
         <v>9.16</v>
       </c>
       <c r="M516">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>7.8000000000000007</v>
       </c>
     </row>
@@ -58273,7 +58442,7 @@
         <v>5.66</v>
       </c>
       <c r="M517">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>2.2999999999999998</v>
       </c>
     </row>
@@ -58315,7 +58484,7 @@
         <v>5.76</v>
       </c>
       <c r="M518">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>3.5999999999999996</v>
       </c>
     </row>
@@ -58357,7 +58526,7 @@
         <v>8.83</v>
       </c>
       <c r="M519">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>8.1999999999999993</v>
       </c>
     </row>
@@ -58399,7 +58568,7 @@
         <v>6.82</v>
       </c>
       <c r="M520">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>6.3</v>
       </c>
     </row>
@@ -58441,7 +58610,7 @@
         <v>5.93</v>
       </c>
       <c r="M521">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>3.6</v>
       </c>
     </row>
@@ -58483,7 +58652,7 @@
         <v>7.96</v>
       </c>
       <c r="M522">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>5.9</v>
       </c>
     </row>
@@ -58525,7 +58694,7 @@
         <v>7.12</v>
       </c>
       <c r="M523">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>5.6999999999999993</v>
       </c>
     </row>
@@ -58567,7 +58736,7 @@
         <v>8.57</v>
       </c>
       <c r="M524">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>8.4</v>
       </c>
     </row>
@@ -58609,7 +58778,7 @@
         <v>8.39</v>
       </c>
       <c r="M525">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>8.6999999999999993</v>
       </c>
     </row>
@@ -58651,7 +58820,7 @@
         <v>7.48</v>
       </c>
       <c r="M526">
-        <f t="shared" ref="M526:M546" si="10">F526+J526</f>
+        <f t="shared" si="8"/>
         <v>4.5999999999999996</v>
       </c>
     </row>
@@ -58693,7 +58862,7 @@
         <v>6.6</v>
       </c>
       <c r="M527">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>2.4000000000000004</v>
       </c>
     </row>
@@ -58735,7 +58904,7 @@
         <v>6.1</v>
       </c>
       <c r="M528">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>3.3</v>
       </c>
     </row>
@@ -58777,7 +58946,7 @@
         <v>6.72</v>
       </c>
       <c r="M529">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>3.9000000000000004</v>
       </c>
     </row>
@@ -58819,7 +58988,7 @@
         <v>5.81</v>
       </c>
       <c r="M530">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
     </row>
@@ -58861,7 +59030,7 @@
         <v>5.6</v>
       </c>
       <c r="M531">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>2.1</v>
       </c>
     </row>
@@ -58903,7 +59072,7 @@
         <v>6.6</v>
       </c>
       <c r="M532">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>2.8000000000000003</v>
       </c>
     </row>
@@ -58945,7 +59114,7 @@
         <v>7.27</v>
       </c>
       <c r="M533">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>4.5999999999999996</v>
       </c>
     </row>
@@ -58987,7 +59156,7 @@
         <v>5.88</v>
       </c>
       <c r="M534">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>2.5</v>
       </c>
     </row>
@@ -59029,7 +59198,7 @@
         <v>7.82</v>
       </c>
       <c r="M535">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>7.6999999999999993</v>
       </c>
     </row>
@@ -59071,7 +59240,7 @@
         <v>6.19</v>
       </c>
       <c r="M536">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>2.4</v>
       </c>
     </row>
@@ -59113,7 +59282,7 @@
         <v>8.35</v>
       </c>
       <c r="M537">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>8.3000000000000007</v>
       </c>
     </row>
@@ -59155,7 +59324,7 @@
         <v>6.13</v>
       </c>
       <c r="M538">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>2.8</v>
       </c>
     </row>
@@ -59197,7 +59366,7 @@
         <v>6.19</v>
       </c>
       <c r="M539">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>2.1</v>
       </c>
     </row>
@@ -59239,7 +59408,7 @@
         <v>7.4</v>
       </c>
       <c r="M540">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>4.7</v>
       </c>
     </row>
@@ -59281,7 +59450,7 @@
         <v>8.67</v>
       </c>
       <c r="M541">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>7.3000000000000007</v>
       </c>
     </row>
@@ -59323,7 +59492,7 @@
         <v>7.83</v>
       </c>
       <c r="M542">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>8.5</v>
       </c>
     </row>
@@ -59365,7 +59534,7 @@
         <v>7.94</v>
       </c>
       <c r="M543">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>6.2</v>
       </c>
     </row>
@@ -59407,7 +59576,7 @@
         <v>5.82</v>
       </c>
       <c r="M544">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>3.5999999999999996</v>
       </c>
     </row>
@@ -59449,7 +59618,7 @@
         <v>6.49</v>
       </c>
       <c r="M545">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>2.4000000000000004</v>
       </c>
     </row>
@@ -59491,12 +59660,20 @@
         <v>5.99</v>
       </c>
       <c r="M546">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>3.3</v>
       </c>
     </row>
+    <row r="547" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A547">
+        <f>SUM(A2:A546)</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L546" xr:uid="{CAE3D4AB-79CA-884A-9A5E-1A19FCA51F34}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M547">
+    <sortCondition ref="A311:A547"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -59506,7 +59683,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
